--- a/sheets/대금율보/검수/우리가 가는길.xlsx
+++ b/sheets/대금율보/검수/우리가 가는길.xlsx
@@ -7350,11 +7350,7 @@
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="27"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
@@ -7375,11 +7371,7 @@
         </is>
       </c>
       <c r="O8" s="27"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="27"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
@@ -7387,11 +7379,7 @@
         </is>
       </c>
       <c r="S8" s="27"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T8" s="21"/>
       <c r="U8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
@@ -7492,11 +7480,7 @@
       <c r="I10" s="26"/>
       <c r="J10" s="21"/>
       <c r="K10" s="25"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="25"/>
       <c r="N10" s="21"/>
       <c r="O10" s="25"/>
@@ -7639,11 +7623,7 @@
       <c r="M13" s="25"/>
       <c r="N13" s="21"/>
       <c r="O13" s="25"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P13" s="21"/>
       <c r="Q13" s="25"/>
       <c r="R13" s="21"/>
       <c r="S13" s="25"/>
@@ -7899,11 +7879,7 @@
         </is>
       </c>
       <c r="C19" s="27"/>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D19" s="21"/>
       <c r="E19" s="27"/>
       <c r="F19" s="21"/>
       <c r="G19" s="27"/>
@@ -8579,7 +8555,7 @@
       <c r="I28" s="27"/>
       <c r="J28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -8596,7 +8572,7 @@
       <c r="M28" s="27"/>
       <c r="N28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/우리가 가는길.xlsx
+++ b/sheets/대금율보/검수/우리가 가는길.xlsx
@@ -6915,32 +6915,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="25"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="U10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="27"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -7630,7 +7630,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7699,10 +7699,10 @@
       </c>
       <c r="U14" s="27"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="25"/>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -8354,7 +8354,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="27"/>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="23" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="25"/>
@@ -8525,7 +8525,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="25"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="23" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
